--- a/output/pdf_financials_xlsx/ELYX.xlsx
+++ b/output/pdf_financials_xlsx/ELYX.xlsx
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000807</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.158117</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.033875</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000807</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.158117</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.033875</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -1390,10 +1390,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.158117</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.033875</v>
+        <v>0</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">

--- a/output/pdf_financials_xlsx/ELYX.xlsx
+++ b/output/pdf_financials_xlsx/ELYX.xlsx
@@ -1101,10 +1101,8 @@
       <c r="D34" s="3" t="n">
         <v>0.033875</v>
       </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E34" s="3" t="n">
+        <v>0.121121</v>
       </c>
     </row>
     <row r="35">
@@ -1122,10 +1120,8 @@
       <c r="D35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1143,10 +1139,8 @@
       <c r="D36" s="3" t="n">
         <v>0.033875</v>
       </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E36" s="3" t="n">
+        <v>0.121121</v>
       </c>
     </row>
     <row r="37">
@@ -1164,10 +1158,8 @@
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1185,10 +1177,8 @@
       <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1206,10 +1196,8 @@
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1227,10 +1215,8 @@
       <c r="D40" s="3" t="n">
         <v>0.007241</v>
       </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E40" s="3" t="n">
+        <v>0.007215</v>
       </c>
     </row>
     <row r="41">
@@ -1248,10 +1234,8 @@
       <c r="D41" s="3" t="n">
         <v>0.007241</v>
       </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E41" s="3" t="n">
+        <v>0.007215</v>
       </c>
     </row>
     <row r="42">
@@ -1269,10 +1253,8 @@
       <c r="D42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1290,10 +1272,8 @@
       <c r="D43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1311,10 +1291,8 @@
       <c r="D44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1332,10 +1310,8 @@
       <c r="D45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1353,10 +1329,8 @@
       <c r="D46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1374,10 +1348,8 @@
       <c r="D47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1395,10 +1367,8 @@
       <c r="D48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1418,10 +1388,8 @@
       <c r="D49" s="3" t="n">
         <v>0.041116</v>
       </c>
-      <c r="E49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E49" s="3" t="n">
+        <v>0.128336</v>
       </c>
     </row>
     <row r="50">
@@ -1439,10 +1407,8 @@
       <c r="D50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1460,10 +1426,8 @@
       <c r="D51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1481,10 +1445,8 @@
       <c r="D52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1502,10 +1464,8 @@
       <c r="D53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1523,10 +1483,8 @@
       <c r="D54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1571,10 +1529,8 @@
       <c r="D56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1592,10 +1548,8 @@
       <c r="D57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1613,10 +1567,8 @@
       <c r="D58" s="3" t="n">
         <v>0.118093</v>
       </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E58" s="3" t="n">
+        <v>0.123313</v>
       </c>
     </row>
     <row r="59">
@@ -1634,10 +1586,8 @@
       <c r="D59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1655,10 +1605,8 @@
       <c r="D60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1676,10 +1624,8 @@
       <c r="D61" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1699,10 +1645,8 @@
       <c r="D62" s="3" t="n">
         <v>0.118093</v>
       </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E62" s="3" t="n">
+        <v>0.123313</v>
       </c>
     </row>
     <row r="63">
@@ -1720,10 +1664,8 @@
       <c r="D63" s="3" t="n">
         <v>0.159209</v>
       </c>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E63" s="3" t="n">
+        <v>0.251649</v>
       </c>
     </row>
     <row r="64">
@@ -1741,10 +1683,8 @@
       <c r="D64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1762,10 +1702,8 @@
       <c r="D65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1783,10 +1721,8 @@
       <c r="D66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1796,18 +1732,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.026845</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.036393</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.05717</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.052685</v>
       </c>
     </row>
     <row r="68">
@@ -1825,10 +1759,8 @@
       <c r="D68" s="3" t="n">
         <v>0.381206</v>
       </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E68" s="3" t="n">
+        <v>0.094127</v>
       </c>
     </row>
     <row r="69">
@@ -1846,10 +1778,8 @@
       <c r="D69" s="3" t="n">
         <v>0.068563</v>
       </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="3" t="n">
+        <v>0.096231</v>
       </c>
     </row>
     <row r="70">
@@ -1867,10 +1797,8 @@
       <c r="D70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1888,10 +1816,8 @@
       <c r="D71" s="3" t="n">
         <v>0.068563</v>
       </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E71" s="3" t="n">
+        <v>0.096231</v>
       </c>
     </row>
     <row r="72">
@@ -1909,10 +1835,8 @@
       <c r="D72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1930,10 +1854,8 @@
       <c r="D73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1951,10 +1873,8 @@
       <c r="D74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1972,10 +1892,8 @@
       <c r="D75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2020,10 +1938,8 @@
       <c r="D77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2041,10 +1957,8 @@
       <c r="D78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2062,10 +1976,8 @@
       <c r="D79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2083,10 +1995,8 @@
       <c r="D80" s="3" t="n">
         <v>-0.2359684746696035</v>
       </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" s="3" t="n">
+        <v>15.2966142107773</v>
       </c>
     </row>
     <row r="81">
@@ -2104,10 +2014,8 @@
       <c r="D81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2125,10 +2033,8 @@
       <c r="D82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2146,10 +2052,8 @@
       <c r="D83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2167,10 +2071,8 @@
       <c r="D84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2188,10 +2090,8 @@
       <c r="D85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2236,10 +2136,8 @@
       <c r="D87" s="3" t="n">
         <v>0.449769</v>
       </c>
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E87" s="3" t="n">
+        <v>0.245358</v>
       </c>
     </row>
     <row r="88">
@@ -2257,10 +2155,8 @@
       <c r="D88" s="3" t="n">
         <v>0.300531</v>
       </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E88" s="3" t="n">
+        <v>0.382118</v>
       </c>
     </row>
     <row r="89">
@@ -2278,10 +2174,8 @@
       <c r="D89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2299,10 +2193,8 @@
       <c r="D90" s="3" t="n">
         <v>-0.6160910000000001</v>
       </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E90" s="3" t="n">
+        <v>-0.457827</v>
       </c>
     </row>
     <row r="91">
@@ -2320,10 +2212,8 @@
       <c r="D91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2341,10 +2231,8 @@
       <c r="D92" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E92" s="3" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="93">
@@ -2362,10 +2250,8 @@
       <c r="D93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2383,10 +2269,8 @@
       <c r="D94" s="3" t="n">
         <v>-0.29056</v>
       </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E94" s="3" t="n">
+        <v>0.006291</v>
       </c>
     </row>
     <row r="95">
@@ -2404,10 +2288,8 @@
       <c r="D95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2425,10 +2307,8 @@
       <c r="D96" s="3" t="n">
         <v>-0.29056</v>
       </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E96" s="3" t="n">
+        <v>0.006291</v>
       </c>
     </row>
     <row r="97">
@@ -2446,10 +2326,8 @@
       <c r="D97" s="3" t="n">
         <v>-1.825022454760723</v>
       </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E97" s="3" t="n">
+        <v>0.02499910589750009</v>
       </c>
     </row>
     <row r="98">
@@ -2509,13 +2387,13 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003232</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004009</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>2.6e-05</v>
       </c>
     </row>
     <row r="102">
@@ -2604,13 +2482,13 @@
         <v>0.04737</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.004637</v>
+        <v>0.001405</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.05464</v>
+        <v>0.050631</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.021365</v>
+        <v>0.021391</v>
       </c>
     </row>
     <row r="107">
@@ -3183,7 +3061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3264,10 +3142,8 @@
       <c r="G2" s="5" t="n">
         <v>0.033875</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H2" s="5" t="n">
+        <v>0.121121</v>
       </c>
     </row>
     <row r="3">
@@ -3302,10 +3178,8 @@
       <c r="G3" s="5" t="n">
         <v>0.007241</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H3" s="5" t="n">
+        <v>0.007215</v>
       </c>
     </row>
     <row r="4">
@@ -3340,10 +3214,8 @@
       <c r="G4" s="5" t="n">
         <v>0.041116</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H4" s="5" t="n">
+        <v>0.128336</v>
       </c>
     </row>
     <row r="5">
@@ -3380,10 +3252,8 @@
       <c r="G5" s="5" t="n">
         <v>0.118093</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H5" s="5" t="n">
+        <v>0.123313</v>
       </c>
     </row>
     <row r="6">
@@ -3416,10 +3286,8 @@
       <c r="G6" s="5" t="n">
         <v>0.159209</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H6" s="5" t="n">
+        <v>0.251649</v>
       </c>
     </row>
     <row r="7">
@@ -3435,7 +3303,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Note 6) $</t>
+          <t>Accounts payable and accrued liabilities (Note 6, 7 and 11) $</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3448,16 +3316,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>0.319691</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G7" s="5" t="n">
         <v>0.381206</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H7" s="5" t="n">
+        <v>0.094127</v>
       </c>
     </row>
     <row r="8">
@@ -3473,7 +3341,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Loans payable (Note 7)</t>
+          <t>Loans payable (Notes 7)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3481,10 +3349,8 @@
           <t>CurrentDebt</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="5" t="n">
+        <v>0.068563</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0.068563</v>
@@ -3492,10 +3358,8 @@
       <c r="G8" s="5" t="n">
         <v>0.068563</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H8" s="5" t="n">
+        <v>0.096231</v>
       </c>
     </row>
     <row r="9">
@@ -3511,27 +3375,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0.376761</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0.388254</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.449769</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred premium on flow-through special warrants (Note 8)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="10">
@@ -3542,32 +3406,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shareholders’ deficit</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Share capital (Note 8)</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.052031</v>
+        <v>0.376761</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.300531</v>
+        <v>0.388254</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.300531</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.449769</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.245358</v>
       </c>
     </row>
     <row r="11">
@@ -3578,30 +3440,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shareholders’ deficit</t>
+          <t>Shareholders’ equity (deficit)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Obligation to issue shares (Note 5)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Share capital (Note 9)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n">
-        <v>0.025</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.300531</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.382118</v>
       </c>
     </row>
     <row r="12">
@@ -3612,32 +3478,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shareholders’ deficit</t>
+          <t>Shareholders’ equity (deficit)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Reserve (Note 10)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>-0.427985</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>-0.552436</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>-0.6160910000000001</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="13">
@@ -3648,32 +3518,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shareholders’ deficit</t>
+          <t>Shareholders’ equity (deficit)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Total shareholders’ deficit</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>-0.375954</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>-0.226905</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>-0.29056</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Subscriptions received (Note 9)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="14">
@@ -3684,32 +3554,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shareholders’ deficit</t>
+          <t>Shareholders’ equity (deficit)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Total liabilities and shareholders’ deficit $</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0.000807</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0.161349</v>
+          <t>Obligation to issue shares (Note 5)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.159209</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="15">
@@ -3720,34 +3588,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Shareholders’ equity (deficit)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Notes 6, 7 and 9) $</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0.308198</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.319691</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>-0.6160910000000001</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>-0.457827</v>
       </c>
     </row>
     <row r="16">
@@ -3758,49 +3626,57 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Shareholders’ equity (deficit)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Loans payable (Notes 7)</t>
+          <t>Total shareholders’ equity (deficit)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CurrentDebt</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>0.068563</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0.068563</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.29056</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.006291</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Shareholders’ equity (deficit)</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>August 31, 2025 August</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Total liabilities and shareholders’ equity (deficit) $</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -3812,126 +3688,138 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.002024</v>
+        <v>0.159209</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.251649</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) $</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities (Note 6) $</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F18" s="5" t="n">
+        <v>0.319691</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.063655</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>0.158264</v>
+        <v>0.381206</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" s="5" t="n">
-        <v>0.005763</v>
+          <t>Loans payable (Note 7)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.006856</v>
+        <v>0.068563</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.006875</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>0.008003</v>
+        <v>0.068563</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders’ deficit</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gain on debt settlement</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>-0.298779</v>
+          <t>Share capital (Note 8)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.052031</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.300531</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.300531</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders’ deficit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Consulting fees settled in shares</t>
+          <t>Obligation to issue shares (Note 5)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -3940,154 +3828,162 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>0.077</v>
+      <c r="F21" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Shareholders’ deficit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GST receivables</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.427985</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.003232</v>
+        <v>-0.552436</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.004009</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>2.6e-05</v>
+        <v>-0.6160910000000001</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Shareholders’ deficit</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Total shareholders’ deficit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.04737</v>
+        <v>-0.375954</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.004637</v>
+        <v>-0.226905</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.04214</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>0.021365</v>
+        <v>-0.29056</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Shareholders’ deficit</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Net cash flows used in operating activities</t>
+          <t>Total liabilities and shareholders’ deficit $</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.01494</v>
+        <v>0.000807</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-0.020417</v>
+        <v>0.161349</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.018649</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>-0.034121</v>
+        <v>0.159209</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Exploration and evaluation asset</t>
+          <t>Accounts payable and accrued liabilities (Notes 6, 7 and 9) $</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.308198</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-0.070773</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>-0.105593</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>-0.00522</v>
+        <v>0.319691</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -4096,34 +3992,28 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Investing activities</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Net cash flows used in investing activities</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>August 31, 2025 August</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="5" t="n">
-        <v>-0.070773</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.105593</v>
+        <v>0.002024</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>-0.00522</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="27">
@@ -4134,12 +4024,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of flow-through special warrants, net of costs</t>
+          <t>Net and comprehensive income (loss) $</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -4153,13 +4043,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G27" s="5" t="n">
+        <v>-0.063655</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.104587</v>
+        <v>0.158264</v>
       </c>
     </row>
     <row r="28">
@@ -4170,32 +4058,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Proceeds from subscriptions received in advance</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="5" t="n">
+        <v>0.005763</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.006856</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.006875</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.002</v>
+        <v>0.008003</v>
       </c>
     </row>
     <row r="29">
@@ -4206,12 +4088,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Proceeds from loan payable</t>
+          <t>Gain on debt settlement</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -4231,7 +4113,7 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.02</v>
+        <v>-0.298779</v>
       </c>
     </row>
     <row r="30">
@@ -4242,24 +4124,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Net cash flows provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0.2485</v>
+          <t>Consulting fees settled in shares</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4267,7 +4149,7 @@
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0.126587</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="31">
@@ -4278,30 +4160,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Change in cash during the year</t>
+          <t>GST receivables</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>6e-05</v>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.15731</v>
+        <v>-0.003232</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.124242</v>
+        <v>-0.004009</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.087246</v>
+        <v>2.6e-05</v>
       </c>
     </row>
     <row r="32">
@@ -4312,30 +4196,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.0007470000000000001</v>
+        <v>0.04737</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.000807</v>
+        <v>0.004637</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.158117</v>
+        <v>0.04214</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.033875</v>
+        <v>0.021365</v>
       </c>
     </row>
     <row r="33">
@@ -4346,30 +4230,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cash, end of the year $</t>
+          <t>Net cash flows used in operating activities</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.000807</v>
+        <v>-0.01494</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.158117</v>
+        <v>-0.020417</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.033875</v>
+        <v>-0.018649</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.121121</v>
+        <v>-0.034121</v>
       </c>
     </row>
     <row r="34">
@@ -4380,17 +4264,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Exploration and evaluation asset costs in accounts payable and accrued liabilities $</t>
+          <t>Exploration and evaluation asset</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4398,18 +4282,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F34" s="5" t="n">
+        <v>-0.070773</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.105593</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>-0.00522</v>
       </c>
     </row>
     <row r="35">
@@ -4420,32 +4300,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Accounts payable converted to loan payable $</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Net cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F35" s="5" t="n">
+        <v>-0.070773</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>-0.105593</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.007668</v>
+        <v>-0.00522</v>
       </c>
     </row>
     <row r="36">
@@ -4456,12 +4336,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Deferred premium on flow-through special warrants $</t>
+          <t>Proceeds from issuance of flow-through special warrants, net of costs</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -4481,7 +4361,7 @@
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.055</v>
+        <v>0.104587</v>
       </c>
     </row>
     <row r="37">
@@ -4492,12 +4372,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Interest and taxes paid $</t>
+          <t>Proceeds from subscriptions received in advance</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -4516,10 +4396,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H37" s="5" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="38">
@@ -4530,12 +4408,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Deficit (552,436) (63,655) (616,091) - - - - -</t>
+          <t>Proceeds from loan payable</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -4549,11 +4427,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n">
-        <v>-0.457827</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0.158264</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="39">
@@ -4564,32 +4444,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>issue shares 25,000 - 25,000 - - - - -</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash flows provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.2485</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0.126587</v>
       </c>
     </row>
     <row r="40">
@@ -4600,30 +4480,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>to                                                                                   Obligation</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>received - - - - - - - 2,000 -   2,000                                                                                                                                                                                                                        statements.                                                                                                                         Subscriptions  $           $            - - - -   - - -                                                                                                                                                                                               financial these Reserve 110,000</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash during the year</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>6e-05</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0.15731</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.055</v>
+        <v>-0.124242</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>-0.055</v>
+        <v>0.087246</v>
       </c>
     </row>
     <row r="41">
@@ -4632,28 +4512,32 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>August 31, 2024 August</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.0007470000000000001</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.000807</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.158117</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.033875</v>
       </c>
     </row>
     <row r="42">
@@ -4664,32 +4548,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Cash, end of the year $</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-0.06807299999999999</v>
+        <v>0.000807</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-0.124451</v>
+        <v>0.158117</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.063655</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.033875</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0.121121</v>
       </c>
     </row>
     <row r="43">
@@ -4700,27 +4582,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation asset</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Exploration and evaluation asset costs in accounts payable and accrued liabilities $</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>0.095773</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.0125</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4736,12 +4622,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares, net of costs</t>
+          <t>Accounts payable converted to loan payable $</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4750,18 +4636,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>0.2485</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H44" s="5" t="n">
+        <v>0.007668</v>
       </c>
     </row>
     <row r="45">
@@ -4777,7 +4663,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Obligation to issue shares $</t>
+          <t>Deferred premium on flow-through special warrants $</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -4786,18 +4672,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="5" t="n">
-        <v>0.025</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H45" s="5" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="46">
@@ -4808,12 +4694,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Balance at August 31, 2022 2,270 $ 52,031 $ - $</t>
+          <t>Interest and taxes paid $</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -4822,11 +4708,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="5" t="n">
-        <v>-0.375954</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>-0.427985</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -4842,12 +4732,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Shares issued for private placements (Note 8) 7,750,000 255,500 -</t>
+          <t>Deficit (552,436) (63,655) (616,091) - - - - -</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -4856,18 +4746,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F47" s="5" t="n">
-        <v>0.2555</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.457827</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.158264</v>
       </c>
     </row>
     <row r="48">
@@ -4878,12 +4766,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Share issuance costs (Note 8) - (7,000) -</t>
+          <t>issue shares 25,000 - 25,000 - - - - -</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4892,13 +4780,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="5" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -4914,12 +4802,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
+          <t>to                                                                                   Obligation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Obligation to issue shares (Note 5) - - 25,000</t>
+          <t>received - - - - - - - 2,000 -   2,000                                                                                                                                                                                                                        statements.                                                                                                                         Subscriptions  $           $            - - - -   - - -                                                                                                                                                                                               financial these Reserve 110,000</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4928,18 +4816,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F49" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>-0.055</v>
       </c>
     </row>
     <row r="50">
@@ -4948,31 +4834,23 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>August 31, 2024 August</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-0.124451</v>
+        <v>0.002023</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.124451</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4988,25 +4866,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Balance at August 31, 2023 7,752,270 300,531 25,000</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>-0.06807299999999999</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>-0.226905</v>
+        <v>-0.124451</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.552436</v>
+        <v>-0.063655</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -5022,12 +4902,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Balance at August 31, 2024 7,752,270 $ 300,531 $ 25,000 $</t>
+          <t>Write-off of exploration and evaluation asset</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -5037,10 +4917,12 @@
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>-0.29056</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-0.6160910000000001</v>
+        <v>0.095773</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -5054,18 +4936,24 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>August 31, 2023 August</t>
+          <t>Proceeds from issuance of shares, net of costs</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>0.002022</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.2485</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -5086,22 +4974,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Proceeds from loan issued</t>
+          <t>Obligation to issue shares $</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -5122,25 +5010,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
+          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Balance at August 31, 2021 2,270 $ 52,031 $ - $</t>
+          <t>Balance at August 31, 2022 2,270 $ 52,031 $ - $</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" s="5" t="n">
-        <v>-0.307881</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>-0.359912</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.375954</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.427985</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -5156,24 +5044,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
+          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>-0.06807299999999999</v>
+          <t>Shares issued for private placements (Note 8) 7,750,000 255,500 -</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>-0.06807299999999999</v>
+        <v>0.2555</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -5194,20 +5080,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
+          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Balance at August 31, 2022 2,270 52,031 -</t>
+          <t>Share issuance costs (Note 8) - (7,000) -</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" s="5" t="n">
-        <v>-0.375954</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>-0.427985</v>
+        <v>-0.007</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -5228,22 +5116,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
+          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Shares issued for private placements (Note 8) 7,750,000 255,500 -</t>
+          <t>Obligation to issue shares (Note 5) - - 25,000</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" s="5" t="n">
-        <v>0.2555</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -5264,27 +5152,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
+          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Share issuance costs (Note 8) - (7,000) -</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" s="5" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>-0.124451</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.124451</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -5300,27 +5190,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
+          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Obligation to issue shares (Note 5) - - 25,000</t>
+          <t>Balance at August 31, 2023 7,752,270 300,531 25,000</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>-0.226905</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>-0.552436</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -5336,25 +5224,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
+          <t>Issued    Share Capital    issue shares           Deficit               Deficit</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Balance at August 31, 2023 7,752,270 $ 300,531 $ 25,000 $</t>
+          <t>Balance at August 31, 2024 7,752,270 $ 300,531 $ 25,000 $</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" s="5" t="n">
-        <v>-0.226905</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>-0.552436</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.29056</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>-0.6160910000000001</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -5365,258 +5253,266 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>August 31, 2025 August</t>
+          <t>August 31, 2023 August</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="H62" s="5" t="n">
+      <c r="E62" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F62" s="5" t="n">
         <v>3.1e-05</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 11) $</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from loan issued</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>0.015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0294</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>0.097443</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Balance at August 31, 2021 2,270 $ 52,031 $ - $</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" s="5" t="n">
-        <v>0.015443</v>
+        <v>-0.307881</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.018521</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0.026022</v>
-      </c>
-      <c r="H64" s="5" t="n">
-        <v>0.030225</v>
+        <v>-0.359912</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Regulatory and filing fees</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
-        <v>0.00267</v>
+        <v>-0.06807299999999999</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.002323</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>0.002071</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>0.003399</v>
+        <v>-0.06807299999999999</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Office and administration</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Balance at August 31, 2022 2,270 52,031 -</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>9.7e-05</v>
+        <v>-0.375954</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.0009779999999999999</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>0.001305</v>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>0.001445</v>
+        <v>-0.427985</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Interest expense (Note 7)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Shares issued for private placements (Note 8) 7,750,000 255,500 -</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" s="5" t="n">
-        <v>0.005763</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>0.006856</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>0.006875</v>
-      </c>
-      <c r="H67" s="5" t="n">
-        <v>0.008003</v>
+        <v>0.2555</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Share issuance costs (Note 8) - (7,000) -</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" s="5" t="n">
-        <v>-0.06807299999999999</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>-0.028678</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>-0.065673</v>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>-0.140515</v>
+        <v>-0.007</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Gain on debt settlement (Note 9)</t>
+          <t>Obligation to issue shares (Note 5) - - 25,000</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5628,39 +5524,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H69" s="5" t="n">
-        <v>0.298779</v>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Issued      Share Capital   issue shares       Deficit             Deficit</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Recovery of GST receivable</t>
+          <t>Balance at August 31, 2023 7,752,270 $ 300,531 $ 25,000 $</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>0.002018</v>
+      <c r="E70" s="5" t="n">
+        <v>-0.226905</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>-0.552436</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5674,14 +5570,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) $</t>
+          <t>August 31, 2025 August</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5696,10 +5588,10 @@
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.063655</v>
+        <v>0.002024</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>0.158264</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="72">
@@ -5710,17 +5602,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Earnings (loss) per share, basic $</t>
+          <t>Consulting fees (Note 11) $</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5734,10 +5626,10 @@
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.0294</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>2e-08</v>
+        <v>0.097443</v>
       </c>
     </row>
     <row r="73">
@@ -5748,34 +5640,30 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0.015443</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>0.018521</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>7.75227</v>
+        <v>0.026022</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>8.465749000000001</v>
+        <v>0.030225</v>
       </c>
     </row>
     <row r="74">
@@ -5786,34 +5674,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Earnings (loss) per share, diluted $</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Regulatory and filing fees</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0.002323</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.002071</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>2e-08</v>
+        <v>0.003399</v>
       </c>
     </row>
     <row r="75">
@@ -5824,34 +5704,30 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, diluted</t>
+          <t>Office and administration</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>9.7e-05</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0.0009779999999999999</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>7.75227</v>
+        <v>0.001305</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>8.773147</v>
+        <v>0.001445</v>
       </c>
     </row>
     <row r="76">
@@ -5860,28 +5736,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>August 31, 2024 August</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest expense (Note 7)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0.005763</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.006856</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006875</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>0.008003</v>
       </c>
     </row>
     <row r="77">
@@ -5897,31 +5777,25 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Consulting fees $</t>
+          <t>Loss before other items</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>-0.06807299999999999</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>-0.028678</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.0294</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.065673</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>-0.140515</v>
       </c>
     </row>
     <row r="78">
@@ -5932,12 +5806,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2,018                           - Recovery of GST receivable</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation asset (Note 5)</t>
+          <t>Gain on debt settlement (Note 9)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -5946,18 +5820,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F78" s="5" t="n">
-        <v>-0.095773</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H78" s="5" t="n">
+        <v>0.298779</v>
       </c>
     </row>
     <row r="79">
@@ -5968,29 +5842,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2,018                           - Recovery of GST receivable</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Recovery of GST receivable</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F79" s="5" t="n">
-        <v>-0.124451</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.063655</v>
+        <v>0.002018</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -6006,34 +5878,30 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2,018                           - Recovery of GST receivable</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Net and comprehensive income (loss) $</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F80" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.063655</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>0.158264</v>
       </c>
     </row>
     <row r="81">
@@ -6044,30 +5912,34 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2,018                           - Recovery of GST receivable</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Earnings (loss) per share, basic $</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F81" s="5" t="n">
-        <v>6.028297</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>7.75227</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>2e-08</v>
       </c>
     </row>
     <row r="82">
@@ -6076,28 +5948,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>August 31, 2023 August</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of common shares outstanding, basic</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>7.75227</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>8.465749000000001</v>
       </c>
     </row>
     <row r="83">
@@ -6108,36 +5988,34 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 9) $</t>
+          <t>Earnings (loss) per share, diluted $</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>0.0441</v>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G83" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>2e-08</v>
       </c>
     </row>
     <row r="84">
@@ -6153,27 +6031,29 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation asset (Note 5)</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding, diluted</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F84" s="5" t="n">
-        <v>-0.095773</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>7.75227</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>8.773147</v>
       </c>
     </row>
     <row r="85">
@@ -6182,31 +6062,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>-0.06807299999999999</v>
+          <t>August 31, 2024 August</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>-0.124451</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6222,29 +6094,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
+          <t>Consulting fees $</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="n">
-        <v>-2.928e-05</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.0294</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -6260,27 +6134,355 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>2,018                           - Recovery of GST receivable</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Write-off of exploration and evaluation asset (Note 5)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>-0.095773</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2,018                           - Recovery of GST receivable</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-0.124451</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>-0.063655</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2,018                           - Recovery of GST receivable</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2,018                           - Recovery of GST receivable</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>6.028297</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>7.75227</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>August 31, 2023 August</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Consulting fees (Note 9) $</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>Other items</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Write-off of exploration and evaluation asset (Note 5)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>-0.095773</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>-0.06807299999999999</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>-0.124451</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>-2.928e-05</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
         <is>
           <t>Weighted average number of common shares outstanding, basic and diluted</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" s="5" t="n">
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" s="5" t="n">
         <v>0.002325</v>
       </c>
-      <c r="F87" s="5" t="n">
+      <c r="F96" s="5" t="n">
         <v>6.028297</v>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
